--- a/rag-mcp/data/corporate/taegeon_beauty/corporate_values.xlsx
+++ b/rag-mcp/data/corporate/taegeon_beauty/corporate_values.xlsx
@@ -367,7 +367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="1" max="1"/>
@@ -421,22 +421,12 @@
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
           <t>published_at</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="inlineStr">
-        <is>
-          <t>synthetic</t>
         </is>
       </c>
     </row>
@@ -463,7 +453,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>태건뷰티 기업가치 — 합성</t>
+          <t>태건뷰티 기업가치</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -476,16 +466,8 @@
           <t>피부색·나이·성별·외모를 정상성이나 사회적 성공의 조건으로 표현하지 않는다. 피부 고민을 이유로 사람의 존엄성을 낮추거나 구매를 압박하지 않는다.</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
+      <c r="H2" s="7" t="str"/>
       <c r="I2" s="7" t="str"/>
-      <c r="J2" s="7" t="str"/>
-      <c r="K2" s="7" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" ht="130" customHeight="1" s="1">
       <c r="A3" s="7" t="inlineStr">
@@ -510,7 +492,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>태건뷰티 기업가치 — 합성</t>
+          <t>태건뷰티 기업가치</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -523,16 +505,8 @@
           <t>전쟁·국가폭력·참사를 제품의 흡수·침투 성능을 강조하는 유머로 소비하지 않는다. 날짜·숫자·슬로건이 결합한 맥락을 함께 검토한다.</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
+      <c r="H3" s="7" t="str"/>
       <c r="I3" s="7" t="str"/>
-      <c r="J3" s="7" t="str"/>
-      <c r="K3" s="7" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4" ht="130" customHeight="1" s="1">
       <c r="A4" s="7" t="inlineStr">
@@ -557,7 +531,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>태건뷰티 기업가치 — 합성</t>
+          <t>태건뷰티 기업가치</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -567,244 +541,206 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>실제 제품 자료가 확인되는 범위에서 설명한다. 이 합성 정책은 제품 효능 시험이나 인증 내역을 제공하지 않는다.</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
+          <t>실제 제품 자료가 확인되는 범위에서 설명한다. 효능 시험 결과나 인증 내역으로 확인되지 않은 효과·인증은 광고에 표현하지 않는다.</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="str"/>
       <c r="I4" s="7" t="str"/>
-      <c r="J4" s="7" t="str"/>
-      <c r="K4" s="7" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty-corporate_values-004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty-corporate_values</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>corporate_values</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>태건뷰티 기업가치 — 합성</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>태건뷰티 기업가치</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>미션</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>피부를 고쳐야 할 결점이 아니라 매일 돌보는 몸의 일부로 본다. 완벽한 피부로의 변신이나 다른 사람처럼 보이게 만드는 것보다 각자의 피부 상태에 맞는 꾸준한 관리를 제안한다.</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty-corporate_values-005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty-corporate_values</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>corporate_values</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>태건뷰티 기업가치 — 합성</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>태건뷰티 기업가치</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>핵심 가치: 투명한 설명</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>성분·사용법·사용 시 주의사항을 쉽고 정확하게 설명하는 것을 우선한다. 기적·마법·즉각 변화 같은 과장된 비유보다 소비자가 스스로 판단할 수 있는 정보를 전달한다.</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty-corporate_values-006</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty-corporate_values</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>corporate_values</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>태건뷰티 기업가치 — 합성</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>태건뷰티 기업가치</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>브랜드 톤</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>차분하고 다정한 말투로 소비자의 선택을 존중한다. 불안·수치심·조급함을 자극하거나 명령조로 몰아붙이는 표현 대신 권유하고 설명하는 표현을 사용한다.</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty-corporate_values-007</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty-corporate_values</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>corporate_values</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>태건뷰티 기업가치 — 합성</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>태건뷰티 기업가치</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>주요 고객</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>나이·성별·피부 타입과 관계없이 피부 관리를 시작하거나 이어가려는 모든 사람을 고객으로 본다. 특정 연령대나 특정 성별만을 위한 브랜드로 소개하지 않는다.</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>1</v>
-      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty-corporate_values-008</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>taegeon_beauty-corporate_values</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>corporate_values</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>태건뷰티 기업가치 — 합성</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>태건뷰티 기업가치</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>구매 경험 약속</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>소비자가 충분히 비교하고 고를 시간을 존중한다. 마감 임박·한정 수량을 반복해 구매를 서두르게 하는 방식보다 필요한 사람이 필요한 때에 고르는 경험을 지향한다.</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>v2</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>1</v>
-      </c>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rag-mcp/data/corporate/taegeon_beauty/corporate_values.xlsx
+++ b/rag-mcp/data/corporate/taegeon_beauty/corporate_values.xlsx
@@ -367,7 +367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="1" max="1"/>
@@ -391,40 +391,30 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>company_id</t>
+          <t>document_type</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>document_id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>section</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>content</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>published_at</t>
         </is>
@@ -438,36 +428,26 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty-corporate_values</t>
+          <t>태건뷰티 기업가치</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>외모 다양성</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>태건뷰티 기업가치</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>외모 다양성</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
           <t>피부색·나이·성별·외모를 정상성이나 사회적 성공의 조건으로 표현하지 않는다. 피부 고민을 이유로 사람의 존엄성을 낮추거나 구매를 압박하지 않는다.</t>
         </is>
       </c>
-      <c r="H2" s="7" t="str"/>
-      <c r="I2" s="7" t="str"/>
+      <c r="F2" s="7" t="str"/>
+      <c r="G2" s="7" t="str"/>
     </row>
     <row r="3" ht="130" customHeight="1" s="1">
       <c r="A3" s="7" t="inlineStr">
@@ -477,36 +457,26 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty-corporate_values</t>
+          <t>태건뷰티 기업가치</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>역사·피해자 존중</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>태건뷰티 기업가치</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>역사·피해자 존중</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
           <t>전쟁·국가폭력·참사를 제품의 흡수·침투 성능을 강조하는 유머로 소비하지 않는다. 날짜·숫자·슬로건이 결합한 맥락을 함께 검토한다.</t>
         </is>
       </c>
-      <c r="H3" s="7" t="str"/>
-      <c r="I3" s="7" t="str"/>
+      <c r="F3" s="7" t="str"/>
+      <c r="G3" s="7" t="str"/>
     </row>
     <row r="4" ht="130" customHeight="1" s="1">
       <c r="A4" s="7" t="inlineStr">
@@ -516,36 +486,26 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty-corporate_values</t>
+          <t>태건뷰티 기업가치</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>제품 소통</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>태건뷰티 기업가치</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>제품 소통</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
           <t>실제 제품 자료가 확인되는 범위에서 설명한다. 효능 시험 결과나 인증 내역으로 확인되지 않은 효과·인증은 광고에 표현하지 않는다.</t>
         </is>
       </c>
-      <c r="H4" s="7" t="str"/>
-      <c r="I4" s="7" t="str"/>
+      <c r="F4" s="7" t="str"/>
+      <c r="G4" s="7" t="str"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -555,36 +515,26 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty-corporate_values</t>
+          <t>태건뷰티 기업가치</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>미션</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>태건뷰티 기업가치</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>미션</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
           <t>피부를 고쳐야 할 결점이 아니라 매일 돌보는 몸의 일부로 본다. 완벽한 피부로의 변신이나 다른 사람처럼 보이게 만드는 것보다 각자의 피부 상태에 맞는 꾸준한 관리를 제안한다.</t>
         </is>
       </c>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -594,36 +544,26 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty-corporate_values</t>
+          <t>태건뷰티 기업가치</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>핵심 가치: 투명한 설명</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>태건뷰티 기업가치</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>핵심 가치: 투명한 설명</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
           <t>성분·사용법·사용 시 주의사항을 쉽고 정확하게 설명하는 것을 우선한다. 기적·마법·즉각 변화 같은 과장된 비유보다 소비자가 스스로 판단할 수 있는 정보를 전달한다.</t>
         </is>
       </c>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -633,36 +573,26 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty-corporate_values</t>
+          <t>태건뷰티 기업가치</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>브랜드 톤</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>태건뷰티 기업가치</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>브랜드 톤</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
           <t>차분하고 다정한 말투로 소비자의 선택을 존중한다. 불안·수치심·조급함을 자극하거나 명령조로 몰아붙이는 표현 대신 권유하고 설명하는 표현을 사용한다.</t>
         </is>
       </c>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -672,36 +602,26 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty-corporate_values</t>
+          <t>태건뷰티 기업가치</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>주요 고객</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>태건뷰티 기업가치</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>주요 고객</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
           <t>나이·성별·피부 타입과 관계없이 피부 관리를 시작하거나 이어가려는 모든 사람을 고객으로 본다. 특정 연령대나 특정 성별만을 위한 브랜드로 소개하지 않는다.</t>
         </is>
       </c>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -711,36 +631,26 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty</t>
+          <t>corporate_values</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>taegeon_beauty-corporate_values</t>
+          <t>태건뷰티 기업가치</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>corporate_values</t>
+          <t>구매 경험 약속</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>태건뷰티 기업가치</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>구매 경험 약속</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
           <t>소비자가 충분히 비교하고 고를 시간을 존중한다. 마감 임박·한정 수량을 반복해 구매를 서두르게 하는 방식보다 필요한 사람이 필요한 때에 고르는 경험을 지향한다.</t>
         </is>
       </c>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
